--- a/artfynd/A 31366-2021 artfynd.xlsx
+++ b/artfynd/A 31366-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31366-2021 artfynd.xlsx
+++ b/artfynd/A 31366-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68258996</v>
+        <v>111939888</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>750</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Klotsporig murkla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Gyromitra sphaerospora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Sacc.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lejondals naturreservat, Upl</t>
+          <t>Upplands-Bro, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653122.0433101204</v>
+        <v>653207</v>
       </c>
       <c r="R2" t="n">
-        <v>6600384.055232089</v>
+        <v>6600027</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-10-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Amanda Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Amanda Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68258972</v>
+        <v>82013866</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2009</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lejondals naturreservat, Upl</t>
+          <t>Tång, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653167.7972128551</v>
+        <v>653302</v>
       </c>
       <c r="R3" t="n">
-        <v>6600048.030944787</v>
+        <v>6600353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68258924</v>
+        <v>68258996</v>
       </c>
       <c r="B4" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653116.895672008</v>
+        <v>653122</v>
       </c>
       <c r="R4" t="n">
-        <v>6600422.967484842</v>
+        <v>6600384</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68258949</v>
+        <v>68258924</v>
       </c>
       <c r="B5" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653245.1753583699</v>
+        <v>653117</v>
       </c>
       <c r="R5" t="n">
-        <v>6600235.121076159</v>
+        <v>6600423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,50 +1063,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68258951</v>
+        <v>82013865</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4398</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lejondals naturreservat, Upl</t>
+          <t>Tång, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653206.0207835322</v>
+        <v>653333</v>
       </c>
       <c r="R6" t="n">
-        <v>6600334.127890488</v>
+        <v>6600460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,27 +1119,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Bro</t>
+          <t>Västra Ryd</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1144,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Möllegård</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68258974</v>
+        <v>68258937</v>
       </c>
       <c r="B7" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1181,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>653184.2444543041</v>
+        <v>653231</v>
       </c>
       <c r="R7" t="n">
-        <v>6600044.127887087</v>
+        <v>6600390</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1221,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1253,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68258941</v>
+        <v>68258940</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1264,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>653300.0183929104</v>
+        <v>653302</v>
       </c>
       <c r="R8" t="n">
-        <v>6600288.166790011</v>
+        <v>6600291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1321,9 @@
           <t>2017-10-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1350,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68258971</v>
+        <v>68258943</v>
       </c>
       <c r="B9" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>653000.112298956</v>
+        <v>653296</v>
       </c>
       <c r="R9" t="n">
-        <v>6600416.18036435</v>
+        <v>6600254</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1415,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1447,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68258943</v>
+        <v>68258944</v>
       </c>
       <c r="B10" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1472,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>653295.8147507842</v>
+        <v>653305</v>
       </c>
       <c r="R10" t="n">
-        <v>6600253.952884775</v>
+        <v>6600258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1515,9 @@
           <t>2017-10-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68258944</v>
+        <v>68258949</v>
       </c>
       <c r="B11" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1569,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>653304.8164007325</v>
+        <v>653245</v>
       </c>
       <c r="R11" t="n">
-        <v>6600257.876636536</v>
+        <v>6600235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1612,9 @@
           <t>2017-10-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68258953</v>
+        <v>68258972</v>
       </c>
       <c r="B12" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>653102.1933865288</v>
+        <v>653168</v>
       </c>
       <c r="R12" t="n">
-        <v>6600434.054369585</v>
+        <v>6600048</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,22 +1706,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68258940</v>
+        <v>68258974</v>
       </c>
       <c r="B13" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1763,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>653301.9474948322</v>
+        <v>653184</v>
       </c>
       <c r="R13" t="n">
-        <v>6600290.785926552</v>
+        <v>6600044</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,22 +1803,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68258937</v>
+        <v>68258971</v>
       </c>
       <c r="B14" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>653231.2265870892</v>
+        <v>653000</v>
       </c>
       <c r="R14" t="n">
-        <v>6600390.028236848</v>
+        <v>6600416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,22 +1900,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-10-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82013866</v>
+        <v>68258951</v>
       </c>
       <c r="B15" t="n">
-        <v>88857</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,34 +1943,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2009</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun jordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Geastrum rufescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tång, Upl</t>
+          <t>Lejondals naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>653301.9646047123</v>
+        <v>653206</v>
       </c>
       <c r="R15" t="n">
-        <v>6600352.773629025</v>
+        <v>6600334</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,22 +1997,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,62 +2017,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Johan Möllegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Johan Möllegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111939888</v>
+        <v>111939910</v>
       </c>
       <c r="B16" t="n">
-        <v>81711</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>750</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klotsporig murkla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gyromitra sphaerospora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Sacc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Upplands-Bro, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>653207</v>
+        <v>653148</v>
       </c>
       <c r="R16" t="n">
-        <v>6600027</v>
+        <v>6600341</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2345,61 +2134,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111939910</v>
+        <v>68258953</v>
       </c>
       <c r="B17" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Upplands-Bro, Upl</t>
+          <t>Lejondals naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>653148</v>
+        <v>653102</v>
       </c>
       <c r="R17" t="n">
-        <v>6600341</v>
+        <v>6600434</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2423,12 +2199,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2017-10-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,27 +2219,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Amanda Johansson</t>
+          <t>Johan Möllegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Amanda Johansson</t>
+          <t>Johan Möllegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111939897</v>
+        <v>111939886</v>
       </c>
       <c r="B18" t="n">
-        <v>98980</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2495,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>653206</v>
+        <v>653180</v>
       </c>
       <c r="R18" t="n">
-        <v>6599944</v>
+        <v>6600113</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,6 +2325,604 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111939890</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Upplands-Bro, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>653293</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6600029</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111939896</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Upplands-Bro, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>653252</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6599963</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>68258954</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lejondals naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>653095</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6600463</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2017-10-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2017-10-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>111939884</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Upplands-Bro, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>653136</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6600192</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>68258941</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lejondals naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>653300</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6600288</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2017-10-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2017-10-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Möllegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111939897</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Upplands-Bro, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>653206</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6599944</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Johansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
